--- a/results/Int Task Remove ACC 0.1/Rando_4_permute.xlsx
+++ b/results/Int Task Remove ACC 0.1/Rando_4_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7320728015823581</v>
+        <v>0.7240298768427149</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7357343266782502</v>
+        <v>0.6979088122479755</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7349898643849239</v>
+        <v>0.720728289020752</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7268076090876308</v>
+        <v>0.7081175075675616</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7266771574380662</v>
+        <v>0.714289031679944</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7286113934148554</v>
+        <v>0.6837776885333683</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7271607164322635</v>
+        <v>0.6829253133571561</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.734935907943481</v>
+        <v>0.6990289206526135</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.734935907943481</v>
+        <v>0.7042490356139833</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7336156826104536</v>
+        <v>0.6955067261143713</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7273137068485067</v>
+        <v>0.6686794468303664</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7334852309608891</v>
+        <v>0.6216997781638964</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.734935907943481</v>
+        <v>0.6188906282442164</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7029602279557202</v>
+        <v>0.5826619512834803</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7148736736277306</v>
+        <v>0.5807973805855161</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.706192150498858</v>
+        <v>0.5778960266203323</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6966357134270946</v>
+        <v>0.5798685102011825</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6951850364445027</v>
+        <v>0.5834829087849283</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.686035663158815</v>
+        <v>0.5834829087849283</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.686035663158815</v>
+        <v>0.5798145537597394</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7174376290856637</v>
+        <v>0.5704739424537477</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7097928892240107</v>
+        <v>0.5541476794632222</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7128246948387591</v>
+        <v>0.5589224830344557</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.704082385339147</v>
+        <v>0.5566194308756516</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6929045230523774</v>
+        <v>0.5595747412822782</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7016400026226929</v>
+        <v>0.5691625960288059</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7030524320012239</v>
+        <v>0.5686790370346086</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7059223682916435</v>
+        <v>0.5814202701373635</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6607738036695845</v>
+        <v>0.5827090777956266</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6291041045143101</v>
+        <v>0.5842519588237223</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6424996448436766</v>
+        <v>0.5916583341529249</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6462287862396048</v>
+        <v>0.5875446677375996</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6346459091455485</v>
+        <v>0.5276844354107246</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6477177108262575</v>
+        <v>0.5084656973631009</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5619795593876012</v>
+        <v>0.5147519642876657</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5373180506835393</v>
+        <v>0.5165557486148904</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.526747369111235</v>
+        <v>0.5107530406845229</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5262952277918019</v>
+        <v>0.5122487952004721</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5174832530133647</v>
+        <v>0.5091562032149843</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5119796959861871</v>
+        <v>0.5091562032149843</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5118492443366226</v>
+        <v>0.5088030958703516</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5149848648766788</v>
+        <v>0.5093945677474346</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5190759925253254</v>
+        <v>0.5047502158257657</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.4979250674797014</v>
+        <v>0.5047502158257657</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.468544760624638</v>
+        <v>0.4908417478062267</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.4611363363166464</v>
+        <v>0.4729480160421379</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.4654344108229791</v>
+        <v>0.4685577374903015</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.4567911352981674</v>
+        <v>0.4685577374903015</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.4492003518779574</v>
+        <v>0.495216317520681</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.4283219410112666</v>
+        <v>0.4956998765148783</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.4318530144575943</v>
+        <v>0.4931898774983882</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.4281375329202592</v>
+        <v>0.5165694084734834</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.4309466828399393</v>
+        <v>0.5187645477494017</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4021803866286376</v>
+        <v>0.5182809887552045</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.4021803866286376</v>
+        <v>0.5669135003114447</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.3900668240282377</v>
+        <v>0.5669135003114447</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.3900668240282377</v>
+        <v>0.5571275776153165</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.386029652821034</v>
+        <v>0.5567744702706838</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.386029652821034</v>
+        <v>0.550488203346119</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.4027021932268957</v>
+        <v>0.5524606869269689</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4141546186713875</v>
+        <v>0.5572354904982024</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4162800926684807</v>
+        <v>0.5609263842900698</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.418875465801178</v>
+        <v>0.5671518648438951</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4410536122130064</v>
+        <v>0.5701454228545826</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4471308833010961</v>
+        <v>0.557887748746025</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4017644439344764</v>
+        <v>0.5761933252466971</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4017644439344764</v>
+        <v>0.5761933252466971</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4144223518998131</v>
+        <v>0.610748669529773</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4092179457758253</v>
+        <v>0.6075707034280781</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.3949700302702467</v>
+        <v>0.580068627129572</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4069442623129965</v>
+        <v>0.5938241047328678</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4069442623129965</v>
+        <v>0.5767465495197194</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4068431793594073</v>
+        <v>0.5520829918368685</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.3990659388694008</v>
+        <v>0.5494964976122567</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.3841138576533456</v>
+        <v>0.5503331639510868</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.3750457605262871</v>
+        <v>0.5503331639510868</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.370124796468107</v>
+        <v>0.5439615229103149</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.3792714377820761</v>
+        <v>0.5197863051721688</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.3935712607503087</v>
+        <v>0.523742883213673</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4090588084232152</v>
+        <v>0.52566141035308</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.3831986471276049</v>
+        <v>0.5651220098569539</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4390906905331716</v>
+        <v>0.5658685211290693</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4615563769683856</v>
+        <v>0.564424674075774</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4872724267558382</v>
+        <v>0.5554153143406659</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4884622004393011</v>
+        <v>0.5292840048519818</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4834264935689386</v>
+        <v>0.5053041230917178</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4813843447092636</v>
+        <v>0.5059652602476259</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4835794839851818</v>
+        <v>0.506226163546755</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4939097520462468</v>
+        <v>0.4995150750199434</v>
       </c>
     </row>
   </sheetData>
